--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,11 +585,10 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 549 of 802 items resolved  (65%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>All-epics progress: 562 of 817 items resolved  (69%)</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -800,18 +799,18 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score)</t>
+          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management)</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 562 of 817 items resolved  (69%)</t>
+          <t>All-epics progress: 574 of 830 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -799,18 +799,18 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management)</t>
+          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow)</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 574 of 830 items resolved  (69%)</t>
+          <t>All-epics progress: 575 of 832 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 575 of 832 items resolved  (69%)</t>
+          <t>All-epics progress: 578 of 835 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 578 of 835 items resolved  (69%)</t>
+          <t>All-epics progress: 579 of 836 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 579 of 836 items resolved  (69%)</t>
+          <t>All-epics progress: 584 of 843 items resolved  (69%)</t>
         </is>
       </c>
     </row>
@@ -799,18 +799,18 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow)</t>
+          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow; Sprint 23 = Settings, Team and access)</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 584 of 843 items resolved  (69%)</t>
+          <t>All-epics progress: 586 of 843 items resolved  (70%)</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>243</v>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 586 of 843 items resolved  (70%)</t>
+          <t>All-epics progress: 601 of 859 items resolved  (70%)</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 601 of 859 items resolved  (70%)</t>
+          <t>All-epics progress: 913 of 1033 items resolved  (88%)</t>
         </is>
       </c>
     </row>
@@ -799,18 +799,18 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow; Sprint 23 = Settings, Team and access)</t>
+          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow; Sprint 23 = Settings, Team and access; Sprint 26 = Requests)</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>169</v>
+        <v>315</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>259</v>
+        <v>421</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -799,14 +799,14 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow; Sprint 23 = Settings, Team and access; Sprint 26 = Requests)</t>
+          <t>UX + UI Optimization (18 per-screen + cross-cutting sprints; Sprint 1 = Operating Score; Sprint 21 = My Work task management; Sprint 22 = Decision Desk decision flow; Sprint 23 = Settings, Team and access)</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
@@ -957,41 +957,74 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Epic 11</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Requests -- new feature (employees ask for material, money or equipment; their manager or the owner approves; approval books the expense in Finance; a General request is a yes, not money)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>DecisionOS_Epic11_Requests.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Testing Plan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Automated + Alpha + Beta + GA</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>See Epic 1 Testing Plan sheet</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Go-Live</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Go-Live Checklist</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Final SaaS-scale readiness</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>See Epic 1 Go-Live Checklist sheet</t>
         </is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 913 of 1033 items resolved  (88%)</t>
+          <t>All-epics progress: 922 of 1042 items resolved  (88%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Requests -- new feature (employees ask for material, money or equipment; their manager or the owner approves; approval books the expense in Finance; a General request is a yes, not money)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>DecisionOS_Epic11_Requests.xlsx</t>
+          <t>DecisionOS_Epic11_New_Features.xlsx</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 922 of 1042 items resolved  (88%)</t>
+          <t>All-epics progress: 927 of 1047 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 927 of 1047 items resolved  (89%)</t>
+          <t>All-epics progress: 947 of 1068 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 947 of 1068 items resolved  (89%)</t>
+          <t>All-epics progress: 965 of 1088 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 965 of 1088 items resolved  (89%)</t>
+          <t>All-epics progress: 973 of 1101 items resolved  (88%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 973 of 1101 items resolved  (88%)</t>
+          <t>All-epics progress: 975 of 1101 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,14 +968,14 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>86</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 975 of 1101 items resolved  (89%)</t>
+          <t>All-epics progress: 976 of 1101 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,14 +968,14 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>86</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 976 of 1101 items resolved  (89%)</t>
+          <t>All-epics progress: 978 of 1101 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,14 +968,14 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>86</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 947 of 1068 items resolved  (89%)</t>
+          <t>All-epics progress: 998 of 1121 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 978 of 1101 items resolved  (89%)</t>
+          <t>All-epics progress: 998 of 1121 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 998 of 1121 items resolved  (89%)</t>
+          <t>All-epics progress: 1004 of 1127 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1004 of 1127 items resolved  (89%)</t>
+          <t>All-epics progress: 1006 of 1129 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1006 of 1129 items resolved  (89%)</t>
+          <t>All-epics progress: 1007 of 1130 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 998 of 1121 items resolved  (89%)</t>
+          <t>All-epics progress: 1028 of 1153 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review; Sprint 10 Onboarding, first-week tour, Dex widget)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1007 of 1130 items resolved  (89%)</t>
+          <t>All-epics progress: 1028 of 1153 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review; Sprint 10 Onboarding, first-week tour, Dex widget)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1028 of 1153 items resolved  (89%)</t>
+          <t>All-epics progress: 1039 of 1164 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review; Sprint 10 Onboarding, first-week tour, Dex widget)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review; Sprint 10 Onboarding, first-week tour, Dex widget; Sprint 11 Decisions to owned work)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1039 of 1164 items resolved  (89%)</t>
+          <t>All-epics progress: 1041 of 1166 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1041 of 1166 items resolved  (89%)</t>
+          <t>All-epics progress: 1046 of 1171 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1046 of 1171 items resolved  (89%)</t>
+          <t>All-epics progress: 1051 of 1176 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1051 of 1176 items resolved  (89%)</t>
+          <t>All-epics progress: 1060 of 1185 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -964,18 +964,18 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review; Sprint 10 Onboarding, first-week tour, Dex widget; Sprint 11 Decisions to owned work)</t>
+          <t>New Features -- one sprint per client-asked feature (Sprint 1 Requests; Sprint 2 Notification history; Sprint 3 Preferred name; Sprint 4 Bugs; Sprint 5 Finance delete; Sprint 6 Admin console redesign; Sprint 7 Admin console v2; Sprint 8 Phone redesign; Sprint 9 Finance periods and bill review; Sprint 10 Onboarding, first-week tour, Dex widget; Sprint 11 Decisions to owned work; Sprint 12 Everything links to CRM)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">

--- a/docs/DecisionOS_Master_Tracker.xlsx
+++ b/docs/DecisionOS_Master_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All-epics progress: 1060 of 1185 items resolved  (89%)</t>
+          <t>All-epics progress: 1065 of 1190 items resolved  (89%)</t>
         </is>
       </c>
     </row>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
